--- a/gte/nodes/LPC/compressor_stage_parameters.xlsx
+++ b/gte/nodes/LPC/compressor_stage_parameters.xlsx
@@ -653,7 +653,7 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C3">
         <v>122</v>
@@ -665,13 +665,13 @@
         <v>35.223425172497393</v>
       </c>
       <c r="F3">
-        <v>38.314355165736856</v>
+        <v>37.135451929868033</v>
       </c>
       <c r="G3">
         <v>19.859932677336676</v>
       </c>
       <c r="H3">
-        <v>1.552112837535145</v>
+        <v>1.6807513403140384</v>
       </c>
       <c r="I3">
         <v>-0.56601906149801651</v>
@@ -680,37 +680,37 @@
         <v>0.27807467103462458</v>
       </c>
       <c r="K3">
-        <v>0.29790629659498014</v>
+        <v>0.30041042805014695</v>
       </c>
       <c r="L3">
-        <v>55.017817675406853</v>
+        <v>46.203926755257434</v>
       </c>
       <c r="M3">
-        <v>38.2398157656776</v>
+        <v>38.332662323688517</v>
       </c>
       <c r="N3">
-        <v>12.016943824435044</v>
+        <v>9.9353496204110883</v>
       </c>
       <c r="O3">
-        <v>8.5539866340265114</v>
+        <v>8.6468331920374286</v>
       </c>
       <c r="P3">
-        <v>27.508908837703427</v>
+        <v>23.101963377628717</v>
       </c>
       <c r="Q3">
-        <v>19.1199078828388</v>
+        <v>19.166331161844258</v>
       </c>
       <c r="R3">
-        <v>50.47069946941933</v>
+        <v>52.796050725470081</v>
       </c>
       <c r="S3">
-        <v>41.131511998334879</v>
+        <v>41.177935277340339</v>
       </c>
       <c r="T3">
-        <v>67.2260744249544</v>
+        <v>79.136850440240934</v>
       </c>
       <c r="U3">
-        <v>53.768635026397817</v>
+        <v>53.643277357675515</v>
       </c>
       <c r="V3">
         <v>0.89795918367346927</v>
@@ -719,25 +719,25 @@
         <v>0.9494949494949495</v>
       </c>
       <c r="X3">
-        <v>0.88318519326277456</v>
+        <v>0.74592000854459362</v>
       </c>
       <c r="Y3">
-        <v>0.7516335082952017</v>
+        <v>0.741649736237892</v>
       </c>
       <c r="Z3">
-        <v>0.247142535287065</v>
+        <v>0.16731910114090526</v>
       </c>
       <c r="AA3">
-        <v>0.19900159032810458</v>
+        <v>0.19562854692619391</v>
       </c>
       <c r="AB3">
-        <v>5.733927529359538</v>
+        <v>7.5538918904121726</v>
       </c>
       <c r="AC3">
-        <v>6.9871329904733033</v>
+        <v>7.0773238040144264</v>
       </c>
       <c r="AD3">
-        <v>72.263107685259371</v>
+        <v>75.4934974034555</v>
       </c>
     </row>
     <row r="4" spans="1:30">
@@ -772,37 +772,37 @@
         <v>0.2667691904621704</v>
       </c>
       <c r="K4">
-        <v>0.28986958799310303</v>
+        <v>0.32017704096510424</v>
       </c>
       <c r="L4">
-        <v>59.236191678803678</v>
+        <v>58.8717351285052</v>
       </c>
       <c r="M4">
-        <v>47.03850576374191</v>
+        <v>48.466024671896484</v>
       </c>
       <c r="N4">
-        <v>12.34867860894826</v>
+        <v>12.272702137824572</v>
       </c>
       <c r="O4">
-        <v>10.338616714177887</v>
+        <v>11.766135622332458</v>
       </c>
       <c r="P4">
-        <v>29.618095839401839</v>
+        <v>29.4358675642526</v>
       </c>
       <c r="Q4">
-        <v>23.519252881870955</v>
+        <v>24.233012335948242</v>
       </c>
       <c r="R4">
-        <v>54.345987538461237</v>
+        <v>54.452239342486777</v>
       </c>
       <c r="S4">
-        <v>42.411913007841662</v>
+        <v>43.125672461918938</v>
       </c>
       <c r="T4">
-        <v>67.1268403887144</v>
+        <v>67.504840269060722</v>
       </c>
       <c r="U4">
-        <v>56.106632673605567</v>
+        <v>54.549488121307277</v>
       </c>
       <c r="V4">
         <v>0.92787234042553191</v>
@@ -811,25 +811,25 @@
         <v>0.9245585874799358</v>
       </c>
       <c r="X4">
-        <v>0.8596316854149838</v>
+        <v>0.85406638105929356</v>
       </c>
       <c r="Y4">
-        <v>0.86279065480754014</v>
+        <v>0.74362380846461684</v>
       </c>
       <c r="Z4">
-        <v>0.22421349994243928</v>
+        <v>0.22053186900934618</v>
       </c>
       <c r="AA4">
-        <v>0.2632361392386009</v>
+        <v>0.22345667577263931</v>
       </c>
       <c r="AB4">
-        <v>6.2914993681729152</v>
+        <v>6.3707174718540385</v>
       </c>
       <c r="AC4">
-        <v>5.5754936556694119</v>
+        <v>6.3132519318104343</v>
       </c>
       <c r="AD4">
-        <v>70.263698701076009</v>
+        <v>71.955202723009322</v>
       </c>
     </row>
     <row r="5" spans="1:30">
@@ -867,31 +867,31 @@
         <v>0.30861065303165713</v>
       </c>
       <c r="L5">
-        <v>61.64654704341563</v>
+        <v>57.392896978887819</v>
       </c>
       <c r="M5">
         <v>41.2596086457625</v>
       </c>
       <c r="N5">
-        <v>12.836528422003383</v>
+        <v>11.950799981899294</v>
       </c>
       <c r="O5">
         <v>9.4387239458067125</v>
       </c>
       <c r="P5">
-        <v>30.823273521707815</v>
+        <v>28.69644848944391</v>
       </c>
       <c r="Q5">
         <v>20.629804322881249</v>
       </c>
       <c r="R5">
-        <v>52.640768733820956</v>
+        <v>53.881865325980783</v>
       </c>
       <c r="S5">
         <v>39.50359310709689</v>
       </c>
       <c r="T5">
-        <v>73.066793451409907</v>
+        <v>77.97007094784712</v>
       </c>
       <c r="U5">
         <v>91.236919909047785</v>
@@ -903,25 +903,25 @@
         <v>0.95833333333333315</v>
       </c>
       <c r="X5">
-        <v>0.89628271737998189</v>
+        <v>0.82867615044056087</v>
       </c>
       <c r="Y5">
         <v>0.77810217631858</v>
       </c>
       <c r="Z5">
-        <v>0.25541071047479513</v>
+        <v>0.20904917753639932</v>
       </c>
       <c r="AA5">
         <v>0.23812401033349226</v>
       </c>
       <c r="AB5">
-        <v>5.8462799702553871</v>
+        <v>6.7947117900124017</v>
       </c>
       <c r="AC5">
         <v>6.2325288066921534</v>
       </c>
       <c r="AD5">
-        <v>70.76914579897543</v>
+        <v>71.935012333307441</v>
       </c>
     </row>
   </sheetData>
@@ -1243,7 +1243,7 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C3">
         <v>122</v>
@@ -1255,13 +1255,13 @@
         <v>38.993078292681723</v>
       </c>
       <c r="F3">
-        <v>45.106015042705039</v>
+        <v>43.71813765677566</v>
       </c>
       <c r="G3">
         <v>23.324193824425013</v>
       </c>
       <c r="H3">
-        <v>1.4945295128771974</v>
+        <v>1.6213399736034573</v>
       </c>
       <c r="I3">
         <v>-0.8205331140053912</v>
@@ -1270,37 +1270,37 @@
         <v>0.33515980408367585</v>
       </c>
       <c r="K3">
-        <v>0.29790629659498014</v>
+        <v>0.29205238380960541</v>
       </c>
       <c r="L3">
-        <v>23.849481351685984</v>
+        <v>18.254102149288979</v>
       </c>
       <c r="M3">
-        <v>40.037311599235686</v>
+        <v>39.803152925219045</v>
       </c>
       <c r="N3">
-        <v>6.323653340462255</v>
+        <v>4.7650031054673283</v>
       </c>
       <c r="O3">
-        <v>9.2247403463195052</v>
+        <v>8.9905816723028646</v>
       </c>
       <c r="P3">
-        <v>11.924740675842992</v>
+        <v>9.12705107464449</v>
       </c>
       <c r="Q3">
-        <v>20.018655799617843</v>
+        <v>19.901576462609523</v>
       </c>
       <c r="R3">
-        <v>31.819010622781366</v>
+        <v>33.058049988984948</v>
       </c>
       <c r="S3">
-        <v>45.252936249211629</v>
+        <v>45.135856912203309</v>
       </c>
       <c r="T3">
-        <v>174.39886991703295</v>
+        <v>227.17500303427823</v>
       </c>
       <c r="U3">
-        <v>56.95312011638692</v>
+        <v>57.274467175910686</v>
       </c>
       <c r="V3">
         <v>0.89795918367346927</v>
@@ -1309,25 +1309,25 @@
         <v>0.9494949494949495</v>
       </c>
       <c r="X3">
-        <v>0.71456336827503386</v>
+        <v>0.58449867383497589</v>
       </c>
       <c r="Y3">
-        <v>0.68193006544544477</v>
+        <v>0.70698806997693642</v>
       </c>
       <c r="Z3">
-        <v>0.21694202868556453</v>
+        <v>0.14338941168560859</v>
       </c>
       <c r="AA3">
-        <v>0.14917261481597055</v>
+        <v>0.15698281519710974</v>
       </c>
       <c r="AB3">
-        <v>6.2873709653910872</v>
+        <v>7.8694809243837112</v>
       </c>
       <c r="AC3">
-        <v>8.6009196874941427</v>
+        <v>8.3142423735269855</v>
       </c>
       <c r="AD3">
-        <v>72.36031010939962</v>
+        <v>76.727324637253361</v>
       </c>
     </row>
     <row r="4" spans="1:30">
@@ -1362,37 +1362,37 @@
         <v>0.33631199488365082</v>
       </c>
       <c r="K4">
-        <v>0.28986958799310303</v>
+        <v>0.31028531713250546</v>
       </c>
       <c r="L4">
-        <v>21.822664132002597</v>
+        <v>22.418256695567639</v>
       </c>
       <c r="M4">
-        <v>49.515924535459519</v>
+        <v>50.564118770067005</v>
       </c>
       <c r="N4">
-        <v>5.7751095115200286</v>
+        <v>5.9327260269935422</v>
       </c>
       <c r="O4">
-        <v>11.259947787675968</v>
+        <v>12.308142022283452</v>
       </c>
       <c r="P4">
-        <v>10.911332066001299</v>
+        <v>11.209128347783819</v>
       </c>
       <c r="Q4">
-        <v>24.757962267729759</v>
+        <v>25.282059385033502</v>
       </c>
       <c r="R4">
-        <v>31.70778000369333</v>
+        <v>31.567600237384326</v>
       </c>
       <c r="S4">
-        <v>46.567191523394726</v>
+        <v>47.091288640698465</v>
       </c>
       <c r="T4">
-        <v>203.44067236457764</v>
+        <v>198.1022100534482</v>
       </c>
       <c r="U4">
-        <v>59.194185407571467</v>
+        <v>58.045323780485624</v>
       </c>
       <c r="V4">
         <v>0.92787234042553191</v>
@@ -1401,25 +1401,25 @@
         <v>0.9245585874799358</v>
       </c>
       <c r="X4">
-        <v>0.65542969461766809</v>
+        <v>0.67015325029210415</v>
       </c>
       <c r="Y4">
-        <v>0.80790957717764089</v>
+        <v>0.72335532787214574</v>
       </c>
       <c r="Z4">
-        <v>0.18222496471564861</v>
+        <v>0.1915823640927927</v>
       </c>
       <c r="AA4">
-        <v>0.20832273949172039</v>
+        <v>0.1805035401674647</v>
       </c>
       <c r="AB4">
-        <v>7.4406451425016025</v>
+        <v>7.21428007582787</v>
       </c>
       <c r="AC4">
-        <v>6.6641320368737977</v>
+        <v>7.3667194487197447</v>
       </c>
       <c r="AD4">
-        <v>73.211112301167375</v>
+        <v>73.606020367527748</v>
       </c>
     </row>
     <row r="5" spans="1:30">
@@ -1457,31 +1457,31 @@
         <v>0.29692319017481894</v>
       </c>
       <c r="L5">
-        <v>20.495058973109956</v>
+        <v>18.639642428771392</v>
       </c>
       <c r="M5">
         <v>44.736221548103167</v>
       </c>
       <c r="N5">
-        <v>5.5492495144526517</v>
+        <v>5.046876265793693</v>
       </c>
       <c r="O5">
         <v>10.353753186651471</v>
       </c>
       <c r="P5">
-        <v>10.247529486554978</v>
+        <v>9.319821214385696</v>
       </c>
       <c r="Q5">
         <v>22.368110774051583</v>
       </c>
       <c r="R5">
-        <v>28.399229381272352</v>
+        <v>28.824564404782681</v>
       </c>
       <c r="S5">
         <v>44.524047325190431</v>
       </c>
       <c r="T5">
-        <v>244.59279667802323</v>
+        <v>268.69168469191959</v>
       </c>
       <c r="U5">
         <v>93.60642402475834</v>
@@ -1493,25 +1493,25 @@
         <v>0.95833333333333315</v>
       </c>
       <c r="X5">
-        <v>0.66365064823219089</v>
+        <v>0.61153825280768548</v>
       </c>
       <c r="Y5">
         <v>0.75463548083932674</v>
       </c>
       <c r="Z5">
-        <v>0.20544387828651586</v>
+        <v>0.17163966051038312</v>
       </c>
       <c r="AA5">
         <v>0.18539971601487398</v>
       </c>
       <c r="AB5">
-        <v>7.4447761016247807</v>
+        <v>8.3524625175926115</v>
       </c>
       <c r="AC5">
         <v>7.5208229532703985</v>
       </c>
       <c r="AD5">
-        <v>72.91153839624333</v>
+        <v>74.775806836548782</v>
       </c>
     </row>
   </sheetData>
@@ -1833,7 +1833,7 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C3">
         <v>122</v>
@@ -1845,13 +1845,13 @@
         <v>42.268110206996866</v>
       </c>
       <c r="F3">
-        <v>51.001098287682318</v>
+        <v>49.431833724984408</v>
       </c>
       <c r="G3">
         <v>26.33663272232776</v>
       </c>
       <c r="H3">
-        <v>1.4573719847989619</v>
+        <v>1.5830028414592463</v>
       </c>
       <c r="I3">
         <v>-0.98770744037043612</v>
@@ -1860,37 +1860,37 @@
         <v>0.356354825656103</v>
       </c>
       <c r="K3">
-        <v>0.29790629659498014</v>
+        <v>0.28611938764440287</v>
       </c>
       <c r="L3">
-        <v>12.53116123664352</v>
+        <v>8.6032424716980245</v>
       </c>
       <c r="M3">
-        <v>40.85110644989016</v>
+        <v>40.360139107428594</v>
       </c>
       <c r="N3">
-        <v>3.5492821843637</v>
+        <v>2.3989708487684269</v>
       </c>
       <c r="O3">
-        <v>9.6063236521265818</v>
+        <v>9.1153563096650227</v>
       </c>
       <c r="P3">
-        <v>6.26558061832176</v>
+        <v>4.3016212358490122</v>
       </c>
       <c r="Q3">
-        <v>20.42555322494508</v>
+        <v>20.180069553714297</v>
       </c>
       <c r="R3">
-        <v>24.106288737990464</v>
+        <v>24.919936784867939</v>
       </c>
       <c r="S3">
-        <v>48.3558404992203</v>
+        <v>48.11035682798952</v>
       </c>
       <c r="T3">
-        <v>369.8653445861662</v>
+        <v>538.16436012171482</v>
       </c>
       <c r="U3">
-        <v>60.557761949236351</v>
+        <v>61.2631522667567</v>
       </c>
       <c r="V3">
         <v>0.89795918367346927</v>
@@ -1899,25 +1899,25 @@
         <v>0.9494949494949495</v>
       </c>
       <c r="X3">
-        <v>0.58350503839921053</v>
+        <v>0.46303141857593272</v>
       </c>
       <c r="Y3">
-        <v>0.62287340923931933</v>
+        <v>0.67615879410479562</v>
       </c>
       <c r="Z3">
-        <v>0.18476363749027813</v>
+        <v>0.12354118169507113</v>
       </c>
       <c r="AA3">
-        <v>0.11700817603437592</v>
+        <v>0.13201984611907813</v>
       </c>
       <c r="AB3">
-        <v>6.8531127009311383</v>
+        <v>7.9088095646531533</v>
       </c>
       <c r="AC3">
-        <v>10.134306189431683</v>
+        <v>9.4336230626909288</v>
       </c>
       <c r="AD3">
-        <v>71.669827463200164</v>
+        <v>75.478796713221726</v>
       </c>
     </row>
     <row r="4" spans="1:30">
@@ -1952,37 +1952,37 @@
         <v>0.35924086430915775</v>
       </c>
       <c r="K4">
-        <v>0.28986958799310303</v>
+        <v>0.30312329373741004</v>
       </c>
       <c r="L4">
-        <v>9.9142926441737256</v>
+        <v>10.815059018939689</v>
       </c>
       <c r="M4">
-        <v>50.644333655598764</v>
+        <v>51.356467804565618</v>
       </c>
       <c r="N4">
-        <v>2.8158253801495619</v>
+        <v>3.0716581370272662</v>
       </c>
       <c r="O4">
-        <v>11.784953300685666</v>
+        <v>12.497087449652513</v>
       </c>
       <c r="P4">
-        <v>4.9571463220868628</v>
+        <v>5.4075295094698443</v>
       </c>
       <c r="Q4">
-        <v>25.322166827799382</v>
+        <v>25.678233902282809</v>
       </c>
       <c r="R4">
-        <v>23.238246903483841</v>
+        <v>23.043696472978567</v>
       </c>
       <c r="S4">
-        <v>49.606158915926841</v>
+        <v>49.962225990410268</v>
       </c>
       <c r="T4">
-        <v>499.10233879735586</v>
+        <v>457.64152869046592</v>
       </c>
       <c r="U4">
-        <v>62.817931326816051</v>
+        <v>62.004774767817025</v>
       </c>
       <c r="V4">
         <v>0.92787234042553191</v>
@@ -1991,25 +1991,25 @@
         <v>0.9245585874799358</v>
       </c>
       <c r="X4">
-        <v>0.497698382147691</v>
+        <v>0.52866277505058279</v>
       </c>
       <c r="Y4">
-        <v>0.75976403060949338</v>
+        <v>0.70245915809986326</v>
       </c>
       <c r="Z4">
-        <v>0.14445754855886969</v>
+        <v>0.16157075756979294</v>
       </c>
       <c r="AA4">
-        <v>0.17104669791228494</v>
+        <v>0.15313673235841324</v>
       </c>
       <c r="AB4">
-        <v>8.4463282707154459</v>
+        <v>8.0244025498148641</v>
       </c>
       <c r="AC4">
-        <v>7.7000534181823506</v>
+        <v>8.2685002504138474</v>
       </c>
       <c r="AD4">
-        <v>74.0184659133669</v>
+        <v>73.434470058840162</v>
       </c>
     </row>
     <row r="5" spans="1:30">
@@ -2047,31 +2047,31 @@
         <v>0.28929783006793691</v>
       </c>
       <c r="L5">
-        <v>9.3050925154452688</v>
+        <v>8.439813012524656</v>
       </c>
       <c r="M5">
         <v>46.209060334508706</v>
       </c>
       <c r="N5">
-        <v>2.7042883696048365</v>
+        <v>2.452816899297408</v>
       </c>
       <c r="O5">
         <v>10.761010827559499</v>
       </c>
       <c r="P5">
-        <v>4.6525462577226344</v>
+        <v>4.219906506262328</v>
       </c>
       <c r="Q5">
         <v>23.104530167254353</v>
       </c>
       <c r="R5">
-        <v>20.519574657182424</v>
+        <v>20.700742938335303</v>
       </c>
       <c r="S5">
         <v>48.0075656263367</v>
       </c>
       <c r="T5">
-        <v>600.0325735144977</v>
+        <v>661.42107292102571</v>
       </c>
       <c r="U5">
         <v>98.301415984922315</v>
@@ -2083,25 +2083,25 @@
         <v>0.95833333333333315</v>
       </c>
       <c r="X5">
-        <v>0.4980259162046633</v>
+        <v>0.46351492544753103</v>
       </c>
       <c r="Y5">
         <v>0.72931781681103847</v>
       </c>
       <c r="Z5">
-        <v>0.15997827869889636</v>
+        <v>0.14117352108881606</v>
       </c>
       <c r="AA5">
         <v>0.1537614974516206</v>
       </c>
       <c r="AB5">
-        <v>9.0288176458304079</v>
+        <v>9.5819002607390971</v>
       </c>
       <c r="AC5">
         <v>8.6275884685101083</v>
       </c>
       <c r="AD5">
-        <v>73.6802138755491</v>
+        <v>74.909699864836867</v>
       </c>
     </row>
   </sheetData>
